--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/mar-2026.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/mar-2026.xlsx
@@ -565,11 +565,11 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>372.98</v>
+        <v>16329.07</v>
       </c>
     </row>
     <row r="3">
@@ -626,11 +626,11 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>14.148</v>
+        <v>619.4</v>
       </c>
     </row>
     <row r="4">
@@ -687,11 +687,11 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>243.534</v>
+        <v>10661.92</v>
       </c>
     </row>
     <row r="5">
@@ -748,11 +748,11 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>829.432</v>
+        <v>36312.53</v>
       </c>
     </row>
     <row r="6">
@@ -809,11 +809,11 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>23652.468</v>
+        <v>1035505.11</v>
       </c>
     </row>
     <row r="7">
@@ -874,11 +874,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>15916.373</v>
+        <v>696818.85</v>
       </c>
     </row>
     <row r="8">
@@ -939,11 +939,11 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>123028.152019058</v>
+        <v>5386172.79</v>
       </c>
     </row>
     <row r="9">
@@ -1004,11 +1004,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>7240.2</v>
+        <v>316975.97</v>
       </c>
     </row>
     <row r="10">
@@ -1065,11 +1065,11 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>28.522</v>
+        <v>1248.69</v>
       </c>
     </row>
     <row r="11">
@@ -1126,11 +1126,11 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>6766.296</v>
+        <v>296228.46</v>
       </c>
     </row>
     <row r="12">
@@ -1187,11 +1187,11 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>272.056</v>
+        <v>11910.61</v>
       </c>
     </row>
     <row r="13">
@@ -1248,11 +1248,11 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>178.811</v>
+        <v>7828.35</v>
       </c>
     </row>
     <row r="14">
@@ -1309,11 +1309,11 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1713.514</v>
+        <v>75017.64999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1370,11 +1370,11 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>244.631</v>
+        <v>10709.95</v>
       </c>
     </row>
     <row r="16">
@@ -1431,11 +1431,11 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>232.564</v>
+        <v>10181.65</v>
       </c>
     </row>
     <row r="17">
@@ -1496,11 +1496,11 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>16626.132</v>
+        <v>727892.1</v>
       </c>
     </row>
     <row r="18">
@@ -1557,11 +1557,11 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>4.388</v>
+        <v>192.11</v>
       </c>
     </row>
     <row r="19">
@@ -1618,11 +1618,11 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>27.93</v>
+        <v>1222.78</v>
       </c>
     </row>
     <row r="20">
@@ -1679,11 +1679,11 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1341.631</v>
+        <v>58736.61</v>
       </c>
     </row>
     <row r="21">
@@ -1740,11 +1740,11 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>824.944</v>
+        <v>36116.05</v>
       </c>
     </row>
   </sheetData>
